--- a/AcompanhamentoFaturados 1.xlsx
+++ b/AcompanhamentoFaturados 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\_BKP Cargas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GBASSI\Documents\Python\.vscode\SendMails\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B85854DA-72D3-48B5-98BF-380F02EB0886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1229F86-CAB3-4B34-97D7-0AD95B0FD643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'21_09'!$A$1:$J$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Mesclado!$A$1:$H$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Planilha1 (2)'!$A$1:$K$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Planilha1 (2)'!$A$1:$L$65</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="235">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -466,85 +466,289 @@
     <t>DIRETÓRIOS</t>
   </si>
   <si>
-    <t>Z:\_BKP Cargas\FATUREEPAGUE</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Hecsolutions</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Hellomed</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Kapam</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\AEGON\MAG_VIDA_INDIVIDUAL</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Mapfre\Captalizacao</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\MAPFRE Imobiliario\DIARIO</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\MAPFRE Mais</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\AEGON\COLETIVO</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\NOSSA_CAIXA</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Mapfre\Psicologica</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Ramos Elementares</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Tokio</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\TS Serviços\Sicredi Conver01</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\TS Serviços\TS Serviços</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Assegurou</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Auto_+_Casa</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Auto_+_Casa\Mapfre</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Yamaha Banco</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Banestes</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Berlanda</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Brasil Cap</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Centauro</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\CNP</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Crefisa</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\Daycoval</t>
-  </si>
-  <si>
-    <t>Z:\_BKP Cargas\METLIFE</t>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\AEGON\COLETIVO</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\AEGON\MAG_VIDA_INDIVIDUAL</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\AMIL</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Assegurou</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Auto_+_Casa\BB</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Auto_+_Casa\Mapfre</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\AXA</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Banestes</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Berlanda</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Brasil Cap</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Centauro</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\CNP</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Crefisa</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Daycoval</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Efeito</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\EQUATORIAL</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\FATUREEPAGUE</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Hecsolutions</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Hellomed</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Incentive</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\INTEGRITY</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Kapam</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\KOVRPICPAY</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\LMMOBILIDADE</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\MAPFRE Educacional\DIARIO</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre Favela</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\MAPFRE Imobiliario\DIARIO</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\MAPFRE Mais</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre\BV</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre\Captalizacao</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre\Psicologica</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mapfre\Vida Seguradora</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Mentore</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\METLIFE</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Naturgy</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\NOSSA_CAIXA</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Oxxy</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Ramos Elementares</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\SAUDAPP</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\SENFF</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Sicoob</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Star Companies</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\SULAMERICA</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Sura</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Swile</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Tokio</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\TS Serviços\Sicredi Conver01</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\TS Serviços\TS Serviços</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\USADOSBR</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\USEDIGI</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Vaticano</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Cargas\Yamaha Banco</t>
+  </si>
+  <si>
+    <t>DIRETÓRIOS BADS</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\AMIL</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Assegurou</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\AXA</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Banestes</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Berlanda</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Brasil_Cap</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Capitalizacao</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Centauro</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\CNP</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Crefisa_Seguros</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Daycoval</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Efeito</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\FATUREEPAGUE</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Hecsolutions</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Hellomed</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Incentive</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Integrity</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\KAPAM</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Kovrpicpay</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\LMMOBILIDADE</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAG_Coletivo</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAG_Individual</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAPFRE_Auto_+_Casa\BB</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAPFRE_Auto_+_Casa\MAPFRE</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAPFRE_BV</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAPFRE_EDUCACIONAL</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Mapfre_Favela</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\MAPFRE_Vida_Seguradora</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Mentore</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Metlife</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Naturgy</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Nossa_Caixa</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Oxxy</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\PSICOLOGICA</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Ramos_Elementares</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Saudapp</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Senff</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Sicoob</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Sura</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\USADOSBR</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\USEDIGI</t>
+  </si>
+  <si>
+    <t>\\VBR006001-002.int.mapfre.net\base$\_ BKP Bases\_BKP Erros\Vaticano</t>
   </si>
 </sst>
 </file>
@@ -554,7 +758,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,6 +777,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -618,10 +830,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -645,8 +858,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -996,23 +1211,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E020160-1EC6-4376-AD82-CC2F813550D2}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="18.6640625" customWidth="1"/>
     <col min="4" max="4" width="22.88671875" customWidth="1"/>
-    <col min="5" max="5" width="43.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.77734375" customWidth="1"/>
-    <col min="8" max="8" width="22.21875" style="8" customWidth="1"/>
-    <col min="9" max="9" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="88" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="85.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.77734375" customWidth="1"/>
+    <col min="9" max="9" width="22.21875" style="8" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1029,30 +1244,33 @@
         <v>139</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C2" t="s">
         <v>118</v>
@@ -1063,911 +1281,1001 @@
       <c r="E2" t="s">
         <v>155</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2"/>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H3" s="6">
+        <v>46010</v>
+      </c>
+      <c r="I3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="5">
+        <v>46287</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I5"/>
+      <c r="J5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>184</v>
+      </c>
+      <c r="H7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I7" t="s">
+        <v>130</v>
+      </c>
+      <c r="J7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>185</v>
+      </c>
+      <c r="G8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H8" s="5">
+        <v>46286</v>
+      </c>
+      <c r="I8" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" s="5">
+        <v>46287</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5">
+        <v>46286</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>191</v>
+      </c>
+      <c r="G11" t="s">
+        <v>126</v>
+      </c>
+      <c r="H11" s="5">
+        <v>46286</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="J11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12"/>
+      <c r="J12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F13" t="s">
+        <v>193</v>
+      </c>
+      <c r="I13"/>
+      <c r="J13" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>143</v>
+      </c>
+      <c r="F14" t="s">
+        <v>194</v>
+      </c>
+      <c r="G14" t="s">
         <v>127</v>
       </c>
-      <c r="G2" s="5">
+      <c r="H14" s="5">
         <v>46244</v>
       </c>
-      <c r="H2" s="8">
+      <c r="I14" s="8">
         <v>0.14583333333333334</v>
       </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="J14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>146</v>
+      </c>
+      <c r="F15" t="s">
+        <v>195</v>
+      </c>
+      <c r="I15"/>
+      <c r="J15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>147</v>
+      </c>
+      <c r="F16" t="s">
+        <v>196</v>
+      </c>
+      <c r="G16" t="s">
+        <v>126</v>
+      </c>
+      <c r="H16" s="5">
+        <v>46286</v>
+      </c>
+      <c r="I16" s="8">
+        <v>0.625</v>
+      </c>
+      <c r="J16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" t="s">
+        <v>197</v>
+      </c>
+      <c r="G17" t="s">
+        <v>126</v>
+      </c>
+      <c r="H17" s="5">
+        <v>46285</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0.65625</v>
+      </c>
+      <c r="J17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" t="s">
+        <v>198</v>
+      </c>
+      <c r="G18" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" s="5">
+        <v>46287</v>
+      </c>
+      <c r="I18" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="J18" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F19" t="s">
+        <v>199</v>
+      </c>
+      <c r="G19" t="s">
+        <v>126</v>
+      </c>
+      <c r="H19" s="5">
+        <v>46286</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0.9375</v>
+      </c>
+      <c r="J19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20" t="s">
+        <v>200</v>
+      </c>
+      <c r="G20" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" s="5">
+        <v>46286</v>
+      </c>
+      <c r="I20" s="8">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="J20" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>151</v>
+      </c>
+      <c r="F21" t="s">
+        <v>201</v>
+      </c>
+      <c r="G21" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" s="5">
+        <v>46287</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F22" t="s">
+        <v>202</v>
+      </c>
+      <c r="G22" t="s">
+        <v>126</v>
+      </c>
+      <c r="H22" s="5">
+        <v>46286</v>
+      </c>
+      <c r="I22" s="8">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>153</v>
+      </c>
+      <c r="F23" t="s">
+        <v>203</v>
+      </c>
+      <c r="G23" t="s">
+        <v>127</v>
+      </c>
+      <c r="H23" s="5">
+        <v>46119</v>
+      </c>
+      <c r="J23" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F24" t="s">
+        <v>204</v>
+      </c>
+      <c r="I24"/>
+      <c r="J24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
         <v>156</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F25" t="s">
+        <v>205</v>
+      </c>
+      <c r="G25" t="s">
         <v>126</v>
       </c>
-      <c r="G3" s="5">
+      <c r="H25" s="5">
+        <v>46286</v>
+      </c>
+      <c r="I25" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J25" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>157</v>
+      </c>
+      <c r="F26" t="s">
+        <v>206</v>
+      </c>
+      <c r="G26" t="s">
+        <v>126</v>
+      </c>
+      <c r="H26" s="5">
         <v>46284</v>
       </c>
-      <c r="H3" s="8">
-        <v>0.625</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="I26" s="8">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J26" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s">
+        <v>158</v>
+      </c>
+      <c r="F27" t="s">
+        <v>207</v>
+      </c>
+      <c r="G27" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="5">
-        <v>46284</v>
-      </c>
-      <c r="H4" s="8">
-        <v>0.625</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F5" t="s">
-        <v>126</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="H27" s="5">
         <v>46286</v>
       </c>
-      <c r="H5" s="8">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="I27" s="10">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J27" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
         <v>159</v>
       </c>
-      <c r="F6" t="s">
-        <v>126</v>
-      </c>
-      <c r="G6" s="5">
-        <v>46286</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0.625</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F28" t="s">
+        <v>208</v>
+      </c>
+      <c r="I28"/>
+      <c r="J28" t="s">
+        <v>18</v>
+      </c>
+      <c r="K28" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
         <v>160</v>
       </c>
-      <c r="F7" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" s="5">
-        <v>46285</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0.65625</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F29" t="s">
+        <v>209</v>
+      </c>
+      <c r="I29"/>
+      <c r="J29" t="s">
+        <v>18</v>
+      </c>
+      <c r="K29" t="s">
+        <v>15</v>
+      </c>
+      <c r="L29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s">
         <v>161</v>
       </c>
-      <c r="F8" t="s">
-        <v>128</v>
-      </c>
-      <c r="G8" s="5">
-        <v>46287</v>
-      </c>
-      <c r="H8" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H9" t="s">
-        <v>130</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F30" t="s">
+        <v>210</v>
+      </c>
+      <c r="H30" s="5">
+        <v>46279</v>
+      </c>
+      <c r="J30" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
         <v>162</v>
       </c>
-      <c r="F10" t="s">
-        <v>126</v>
-      </c>
-      <c r="G10" s="5">
-        <v>46286</v>
-      </c>
-      <c r="H10" s="8">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>163</v>
-      </c>
-      <c r="F11" t="s">
-        <v>128</v>
-      </c>
-      <c r="G11" s="5">
-        <v>46287</v>
-      </c>
-      <c r="H11" s="8">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>164</v>
-      </c>
-      <c r="F12" t="s">
-        <v>126</v>
-      </c>
-      <c r="G12" s="5">
-        <v>46286</v>
-      </c>
-      <c r="H12" s="8">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="I12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" t="s">
-        <v>18</v>
-      </c>
-      <c r="K12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>165</v>
-      </c>
-      <c r="F13" t="s">
-        <v>127</v>
-      </c>
-      <c r="G13" s="5">
-        <v>46119</v>
-      </c>
-      <c r="I13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" t="s">
-        <v>18</v>
-      </c>
-      <c r="K13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" t="s">
-        <v>118</v>
-      </c>
-      <c r="D14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" t="s">
-        <v>140</v>
-      </c>
-      <c r="F14" t="s">
-        <v>128</v>
-      </c>
-      <c r="G14" s="5">
-        <v>46286</v>
-      </c>
-      <c r="H14" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="I14" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" t="s">
-        <v>18</v>
-      </c>
-      <c r="K14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s">
-        <v>141</v>
-      </c>
-      <c r="F15" t="s">
-        <v>126</v>
-      </c>
-      <c r="G15" s="5">
-        <v>46284</v>
-      </c>
-      <c r="H15" s="8">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="I15" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" t="s">
-        <v>136</v>
-      </c>
-      <c r="C16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" t="s">
-        <v>142</v>
-      </c>
-      <c r="F16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G16" s="5">
-        <v>46286</v>
-      </c>
-      <c r="H16" s="10">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="I16" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" t="s">
-        <v>136</v>
-      </c>
-      <c r="C17" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" t="s">
-        <v>143</v>
-      </c>
-      <c r="F17" t="s">
-        <v>128</v>
-      </c>
-      <c r="G17" s="5">
-        <v>46279</v>
-      </c>
-      <c r="I17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="5">
-        <v>46197</v>
-      </c>
-      <c r="H18" t="s">
-        <v>118</v>
-      </c>
-      <c r="I18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" t="s">
-        <v>18</v>
-      </c>
-      <c r="K18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" t="s">
-        <v>130</v>
-      </c>
-      <c r="H19" t="s">
-        <v>130</v>
-      </c>
-      <c r="I19" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" t="s">
-        <v>18</v>
-      </c>
-      <c r="K19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>137</v>
-      </c>
-      <c r="C20" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20"/>
-      <c r="I20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" t="s">
-        <v>15</v>
-      </c>
-      <c r="K20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s">
-        <v>137</v>
-      </c>
-      <c r="C21" t="s">
-        <v>118</v>
-      </c>
-      <c r="D21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21"/>
-      <c r="I21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" t="s">
-        <v>130</v>
-      </c>
-      <c r="H22" t="s">
-        <v>130</v>
-      </c>
-      <c r="I22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
-      <c r="C23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23"/>
-      <c r="I23" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" t="s">
-        <v>137</v>
-      </c>
-      <c r="C24" t="s">
-        <v>118</v>
-      </c>
-      <c r="D24" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24"/>
-      <c r="I24" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" t="s">
-        <v>15</v>
-      </c>
-      <c r="K24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25"/>
-      <c r="I25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J25" t="s">
-        <v>18</v>
-      </c>
-      <c r="K25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" t="s">
-        <v>138</v>
-      </c>
-      <c r="C26" t="s">
-        <v>118</v>
-      </c>
-      <c r="D26" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26"/>
-      <c r="I26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" t="s">
-        <v>18</v>
-      </c>
-      <c r="K26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" t="s">
-        <v>118</v>
-      </c>
-      <c r="D27" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" t="s">
-        <v>130</v>
-      </c>
-      <c r="H27" t="s">
-        <v>130</v>
-      </c>
-      <c r="I27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" t="s">
-        <v>18</v>
-      </c>
-      <c r="K27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28" t="s">
-        <v>136</v>
-      </c>
-      <c r="C28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" t="s">
-        <v>144</v>
-      </c>
-      <c r="F28" t="s">
-        <v>128</v>
-      </c>
-      <c r="G28" s="5">
-        <v>46286</v>
-      </c>
-      <c r="H28" s="8">
-        <v>0.9375</v>
-      </c>
-      <c r="I28" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" t="s">
-        <v>18</v>
-      </c>
-      <c r="K28" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" t="s">
-        <v>138</v>
-      </c>
-      <c r="C29" t="s">
-        <v>118</v>
-      </c>
-      <c r="D29" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29"/>
-      <c r="I29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J29" t="s">
-        <v>18</v>
-      </c>
-      <c r="K29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" t="s">
-        <v>130</v>
-      </c>
-      <c r="H30" t="s">
-        <v>130</v>
-      </c>
-      <c r="I30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J30" t="s">
-        <v>18</v>
-      </c>
-      <c r="K30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" t="s">
-        <v>137</v>
-      </c>
-      <c r="C31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31"/>
-      <c r="I31" t="s">
-        <v>18</v>
-      </c>
+      <c r="F31" t="s">
+        <v>211</v>
+      </c>
+      <c r="I31"/>
       <c r="J31" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K31" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1980,20 +2288,26 @@
       <c r="D32" t="s">
         <v>13</v>
       </c>
-      <c r="H32"/>
-      <c r="I32" t="s">
-        <v>18</v>
-      </c>
+      <c r="E32" t="s">
+        <v>163</v>
+      </c>
+      <c r="F32" t="s">
+        <v>212</v>
+      </c>
+      <c r="I32"/>
       <c r="J32" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K32" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B33" t="s">
         <v>136</v>
@@ -2005,340 +2319,405 @@
         <v>13</v>
       </c>
       <c r="E33" t="s">
+        <v>140</v>
+      </c>
+      <c r="F33" t="s">
+        <v>213</v>
+      </c>
+      <c r="G33" t="s">
+        <v>126</v>
+      </c>
+      <c r="H33" s="5">
+        <v>46286</v>
+      </c>
+      <c r="I33" s="8">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="J33" t="s">
+        <v>15</v>
+      </c>
+      <c r="K33" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>141</v>
+      </c>
+      <c r="F34" t="s">
+        <v>214</v>
+      </c>
+      <c r="G34" t="s">
+        <v>126</v>
+      </c>
+      <c r="H34" s="5">
+        <v>46286</v>
+      </c>
+      <c r="I34" s="8">
+        <v>0.9375</v>
+      </c>
+      <c r="J34" t="s">
+        <v>15</v>
+      </c>
+      <c r="K34" t="s">
+        <v>18</v>
+      </c>
+      <c r="L34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>144</v>
+      </c>
+      <c r="F35" t="s">
+        <v>215</v>
+      </c>
+      <c r="G35" t="s">
+        <v>126</v>
+      </c>
+      <c r="H35" s="5">
+        <v>46284</v>
+      </c>
+      <c r="I35" s="8">
+        <v>0.625</v>
+      </c>
+      <c r="J35" t="s">
+        <v>15</v>
+      </c>
+      <c r="K35" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" t="s">
+        <v>136</v>
+      </c>
+      <c r="C36" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
         <v>145</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F36" t="s">
+        <v>216</v>
+      </c>
+      <c r="G36" t="s">
+        <v>126</v>
+      </c>
+      <c r="H36" s="5">
+        <v>46284</v>
+      </c>
+      <c r="I36" s="8">
+        <v>0.625</v>
+      </c>
+      <c r="J36" t="s">
+        <v>15</v>
+      </c>
+      <c r="K36" t="s">
+        <v>18</v>
+      </c>
+      <c r="L36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" t="s">
+        <v>138</v>
+      </c>
+      <c r="C37" t="s">
+        <v>118</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>168</v>
+      </c>
+      <c r="F37" t="s">
+        <v>217</v>
+      </c>
+      <c r="I37"/>
+      <c r="J37" t="s">
+        <v>18</v>
+      </c>
+      <c r="K37" t="s">
+        <v>18</v>
+      </c>
+      <c r="L37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" t="s">
+        <v>164</v>
+      </c>
+      <c r="F38" t="s">
+        <v>218</v>
+      </c>
+      <c r="H38" t="s">
+        <v>130</v>
+      </c>
+      <c r="I38" t="s">
+        <v>130</v>
+      </c>
+      <c r="J38" t="s">
+        <v>15</v>
+      </c>
+      <c r="K38" t="s">
+        <v>18</v>
+      </c>
+      <c r="L38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
+        <v>137</v>
+      </c>
+      <c r="C39" t="s">
+        <v>118</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>165</v>
+      </c>
+      <c r="F39" t="s">
+        <v>219</v>
+      </c>
+      <c r="I39"/>
+      <c r="J39" t="s">
+        <v>18</v>
+      </c>
+      <c r="K39" t="s">
+        <v>15</v>
+      </c>
+      <c r="L39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>171</v>
+      </c>
+      <c r="F40" t="s">
+        <v>220</v>
+      </c>
+      <c r="I40"/>
+      <c r="J40" t="s">
+        <v>18</v>
+      </c>
+      <c r="K40" t="s">
+        <v>15</v>
+      </c>
+      <c r="L40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s">
+        <v>138</v>
+      </c>
+      <c r="C41" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
+        <v>172</v>
+      </c>
+      <c r="F41" t="s">
+        <v>221</v>
+      </c>
+      <c r="I41"/>
+      <c r="J41" t="s">
+        <v>18</v>
+      </c>
+      <c r="K41" t="s">
+        <v>18</v>
+      </c>
+      <c r="L41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" t="s">
+        <v>118</v>
+      </c>
+      <c r="D42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" t="s">
+        <v>173</v>
+      </c>
+      <c r="F42" t="s">
+        <v>222</v>
+      </c>
+      <c r="G42" t="s">
+        <v>126</v>
+      </c>
+      <c r="H42" s="6">
+        <v>46265</v>
+      </c>
+      <c r="J42" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" t="s">
+        <v>18</v>
+      </c>
+      <c r="L42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" t="s">
+        <v>137</v>
+      </c>
+      <c r="C43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" t="s">
+        <v>174</v>
+      </c>
+      <c r="F43" t="s">
+        <v>223</v>
+      </c>
+      <c r="I43"/>
+      <c r="J43" t="s">
+        <v>18</v>
+      </c>
+      <c r="K43" t="s">
+        <v>15</v>
+      </c>
+      <c r="L43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s">
+        <v>175</v>
+      </c>
+      <c r="F44" t="s">
+        <v>224</v>
+      </c>
+      <c r="G44" t="s">
         <v>128</v>
       </c>
-      <c r="G33" s="5">
-        <v>46286</v>
-      </c>
-      <c r="H33" s="8">
-        <v>0.9375</v>
-      </c>
-      <c r="I33" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" t="s">
-        <v>18</v>
-      </c>
-      <c r="K33" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>78</v>
-      </c>
-      <c r="B34" t="s">
-        <v>136</v>
-      </c>
-      <c r="C34" t="s">
-        <v>118</v>
-      </c>
-      <c r="D34" t="s">
-        <v>79</v>
-      </c>
-      <c r="G34" t="s">
-        <v>130</v>
-      </c>
-      <c r="H34" t="s">
-        <v>130</v>
-      </c>
-      <c r="I34" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" t="s">
-        <v>18</v>
-      </c>
-      <c r="K34" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>81</v>
-      </c>
-      <c r="B35" t="s">
-        <v>136</v>
-      </c>
-      <c r="C35" t="s">
-        <v>118</v>
-      </c>
-      <c r="D35" t="s">
-        <v>79</v>
-      </c>
-      <c r="E35" t="s">
-        <v>146</v>
-      </c>
-      <c r="F35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G35" s="6">
-        <v>46010</v>
-      </c>
-      <c r="H35" t="s">
-        <v>130</v>
-      </c>
-      <c r="I35" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" t="s">
-        <v>18</v>
-      </c>
-      <c r="K35" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" t="s">
-        <v>136</v>
-      </c>
-      <c r="C36" t="s">
-        <v>118</v>
-      </c>
-      <c r="D36" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" t="s">
-        <v>147</v>
-      </c>
-      <c r="F36" t="s">
-        <v>128</v>
-      </c>
-      <c r="G36" s="5">
-        <v>46284</v>
-      </c>
-      <c r="H36" s="9">
-        <v>0.125</v>
-      </c>
-      <c r="I36" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" t="s">
-        <v>18</v>
-      </c>
-      <c r="K36" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>86</v>
-      </c>
-      <c r="B37" t="s">
-        <v>137</v>
-      </c>
-      <c r="C37" t="s">
-        <v>118</v>
-      </c>
-      <c r="D37" t="s">
-        <v>13</v>
-      </c>
-      <c r="H37"/>
-      <c r="I37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" t="s">
-        <v>15</v>
-      </c>
-      <c r="K37" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>88</v>
-      </c>
-      <c r="B38" t="s">
-        <v>137</v>
-      </c>
-      <c r="C38" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38"/>
-      <c r="I38" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" t="s">
-        <v>15</v>
-      </c>
-      <c r="K38" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>91</v>
-      </c>
-      <c r="B39" t="s">
-        <v>138</v>
-      </c>
-      <c r="C39" t="s">
-        <v>118</v>
-      </c>
-      <c r="D39" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39"/>
-      <c r="I39" t="s">
-        <v>18</v>
-      </c>
-      <c r="J39" t="s">
-        <v>18</v>
-      </c>
-      <c r="K39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>93</v>
-      </c>
-      <c r="B40" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" t="s">
-        <v>166</v>
-      </c>
-      <c r="F40" t="s">
-        <v>126</v>
-      </c>
-      <c r="G40" s="6">
-        <v>46265</v>
-      </c>
-      <c r="I40" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" t="s">
-        <v>18</v>
-      </c>
-      <c r="K40" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" t="s">
-        <v>137</v>
-      </c>
-      <c r="C41" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" t="s">
-        <v>13</v>
-      </c>
-      <c r="H41"/>
-      <c r="I41" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="H44" s="5">
+        <v>46287</v>
+      </c>
+      <c r="I44" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="J44" t="s">
+        <v>15</v>
+      </c>
+      <c r="K44" t="s">
+        <v>18</v>
+      </c>
+      <c r="L44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>98</v>
-      </c>
-      <c r="B42" t="s">
-        <v>137</v>
-      </c>
-      <c r="C42" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" t="s">
-        <v>13</v>
-      </c>
-      <c r="H42"/>
-      <c r="I42" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" t="s">
-        <v>15</v>
-      </c>
-      <c r="K42" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>95</v>
-      </c>
-      <c r="B43" t="s">
-        <v>136</v>
-      </c>
-      <c r="C43" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" t="s">
-        <v>148</v>
-      </c>
-      <c r="F43" t="s">
-        <v>128</v>
-      </c>
-      <c r="G43" s="5">
-        <v>46286</v>
-      </c>
-      <c r="H43" s="8">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="I43" t="s">
-        <v>15</v>
-      </c>
-      <c r="J43" t="s">
-        <v>18</v>
-      </c>
-      <c r="K43" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" t="s">
-        <v>138</v>
-      </c>
-      <c r="C44" t="s">
-        <v>118</v>
-      </c>
-      <c r="D44" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44"/>
-      <c r="I44" t="s">
-        <v>18</v>
-      </c>
-      <c r="J44" t="s">
-        <v>18</v>
-      </c>
-      <c r="K44" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>104</v>
       </c>
       <c r="B45" t="s">
         <v>137</v>
@@ -2349,20 +2728,26 @@
       <c r="D45" t="s">
         <v>13</v>
       </c>
-      <c r="H45"/>
-      <c r="I45" t="s">
-        <v>18</v>
-      </c>
+      <c r="E45" t="s">
+        <v>176</v>
+      </c>
+      <c r="F45" t="s">
+        <v>225</v>
+      </c>
+      <c r="I45"/>
       <c r="J45" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K45" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s">
         <v>136</v>
@@ -2374,30 +2759,33 @@
         <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="F46" t="s">
+        <v>226</v>
+      </c>
+      <c r="G46" t="s">
         <v>128</v>
       </c>
-      <c r="G46" s="5">
+      <c r="H46" s="5">
         <v>46287</v>
       </c>
-      <c r="H46" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="I46" t="s">
-        <v>15</v>
+      <c r="I46" s="8">
+        <v>0.375</v>
       </c>
       <c r="J46" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K46" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B47" t="s">
         <v>136</v>
@@ -2409,57 +2797,61 @@
         <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="F47" t="s">
-        <v>128</v>
-      </c>
-      <c r="G47" s="5">
-        <v>46287</v>
-      </c>
-      <c r="H47" s="8">
-        <v>0.375</v>
-      </c>
-      <c r="I47" t="s">
-        <v>15</v>
+        <v>227</v>
+      </c>
+      <c r="G47" t="s">
+        <v>126</v>
+      </c>
+      <c r="H47" s="5">
+        <v>46286</v>
+      </c>
+      <c r="I47" s="8">
+        <v>0.66666666666666663</v>
       </c>
       <c r="J47" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K47" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L47" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B48" t="s">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="C48" t="s">
         <v>118</v>
       </c>
       <c r="D48" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" t="s">
-        <v>130</v>
-      </c>
-      <c r="H48" t="s">
-        <v>130</v>
-      </c>
-      <c r="I48" t="s">
-        <v>18</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>178</v>
+      </c>
+      <c r="F48" t="s">
+        <v>228</v>
+      </c>
+      <c r="I48"/>
       <c r="J48" t="s">
         <v>18</v>
       </c>
       <c r="K48" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>105</v>
       </c>
@@ -2472,18 +2864,24 @@
       <c r="D49" t="s">
         <v>13</v>
       </c>
-      <c r="H49"/>
-      <c r="I49" t="s">
-        <v>18</v>
-      </c>
+      <c r="E49" t="s">
+        <v>179</v>
+      </c>
+      <c r="F49" t="s">
+        <v>229</v>
+      </c>
+      <c r="I49"/>
       <c r="J49" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K49" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>106</v>
       </c>
@@ -2496,20 +2894,26 @@
       <c r="D50" t="s">
         <v>13</v>
       </c>
-      <c r="H50"/>
-      <c r="I50" t="s">
-        <v>18</v>
-      </c>
+      <c r="E50" t="s">
+        <v>180</v>
+      </c>
+      <c r="F50" t="s">
+        <v>230</v>
+      </c>
+      <c r="I50"/>
       <c r="J50" t="s">
         <v>18</v>
       </c>
       <c r="K50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="L50" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B51" t="s">
         <v>138</v>
@@ -2520,52 +2924,59 @@
       <c r="D51" t="s">
         <v>13</v>
       </c>
-      <c r="H51"/>
-      <c r="I51" t="s">
-        <v>18</v>
-      </c>
+      <c r="E51" t="s">
+        <v>183</v>
+      </c>
+      <c r="F51" t="s">
+        <v>231</v>
+      </c>
+      <c r="I51"/>
       <c r="J51" t="s">
         <v>18</v>
       </c>
       <c r="K51" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="L51" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="C52" t="s">
         <v>118</v>
       </c>
       <c r="D52" t="s">
-        <v>20</v>
-      </c>
-      <c r="G52" t="s">
-        <v>130</v>
-      </c>
-      <c r="H52" t="s">
-        <v>130</v>
-      </c>
-      <c r="I52" t="s">
-        <v>18</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F52" t="s">
+        <v>232</v>
+      </c>
+      <c r="I52"/>
       <c r="J52" t="s">
         <v>18</v>
       </c>
       <c r="K52" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="L52" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C53" t="s">
         <v>118</v>
@@ -2573,20 +2984,26 @@
       <c r="D53" t="s">
         <v>13</v>
       </c>
-      <c r="H53"/>
-      <c r="I53" t="s">
-        <v>18</v>
-      </c>
+      <c r="E53" t="s">
+        <v>189</v>
+      </c>
+      <c r="F53" t="s">
+        <v>233</v>
+      </c>
+      <c r="I53"/>
       <c r="J53" t="s">
         <v>18</v>
       </c>
       <c r="K53" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B54" t="s">
         <v>138</v>
@@ -2597,23 +3014,29 @@
       <c r="D54" t="s">
         <v>13</v>
       </c>
-      <c r="H54"/>
-      <c r="I54" t="s">
-        <v>18</v>
-      </c>
+      <c r="E54" t="s">
+        <v>190</v>
+      </c>
+      <c r="F54" t="s">
+        <v>234</v>
+      </c>
+      <c r="I54"/>
       <c r="J54" t="s">
         <v>18</v>
       </c>
       <c r="K54" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="L54" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="C55" t="s">
         <v>118</v>
@@ -2621,132 +3044,141 @@
       <c r="D55" t="s">
         <v>13</v>
       </c>
-      <c r="H55"/>
+      <c r="H55" s="5">
+        <v>46197</v>
+      </c>
       <c r="I55" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="J55" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K55" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="B56" t="s">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="C56" t="s">
         <v>118</v>
       </c>
       <c r="D56" t="s">
-        <v>13</v>
-      </c>
-      <c r="H56"/>
+        <v>20</v>
+      </c>
+      <c r="H56" t="s">
+        <v>130</v>
+      </c>
       <c r="I56" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="J56" t="s">
         <v>18</v>
       </c>
       <c r="K56" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="L56" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="B57" t="s">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="C57" t="s">
         <v>118</v>
       </c>
       <c r="D57" t="s">
-        <v>13</v>
-      </c>
-      <c r="H57"/>
+        <v>20</v>
+      </c>
+      <c r="H57" t="s">
+        <v>130</v>
+      </c>
       <c r="I57" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="J57" t="s">
         <v>18</v>
       </c>
       <c r="K57" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="L57" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="C58" t="s">
         <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" t="s">
-        <v>130</v>
+        <v>13</v>
       </c>
       <c r="H58" t="s">
         <v>130</v>
       </c>
       <c r="I58" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="J58" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="L58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="B59" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="C59" t="s">
         <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" t="s">
-        <v>151</v>
-      </c>
-      <c r="F59" t="s">
-        <v>128</v>
-      </c>
-      <c r="G59" s="5">
-        <v>46286</v>
-      </c>
-      <c r="H59" s="8">
-        <v>0.66666666666666663</v>
+        <v>20</v>
+      </c>
+      <c r="H59" t="s">
+        <v>130</v>
       </c>
       <c r="I59" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="J59" t="s">
         <v>18</v>
       </c>
       <c r="K59" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="L59" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="B60" t="s">
         <v>20</v>
@@ -2757,84 +3189,69 @@
       <c r="D60" t="s">
         <v>20</v>
       </c>
-      <c r="G60" t="s">
-        <v>130</v>
-      </c>
       <c r="H60" t="s">
         <v>130</v>
       </c>
       <c r="I60" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="J60" t="s">
         <v>18</v>
       </c>
       <c r="K60" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="L60" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="C61" t="s">
         <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" t="s">
-        <v>152</v>
-      </c>
-      <c r="F61" t="s">
-        <v>126</v>
-      </c>
-      <c r="G61" s="5">
-        <v>46286</v>
-      </c>
-      <c r="H61" s="8">
-        <v>0.58333333333333337</v>
+        <v>20</v>
+      </c>
+      <c r="H61" t="s">
+        <v>130</v>
       </c>
       <c r="I61" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="J61" t="s">
         <v>18</v>
       </c>
       <c r="K61" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="L61" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B62" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="C62" t="s">
         <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" t="s">
-        <v>153</v>
-      </c>
-      <c r="F62" t="s">
-        <v>128</v>
-      </c>
-      <c r="G62" s="5">
-        <v>46287</v>
-      </c>
-      <c r="H62" s="8">
-        <v>0.33333333333333331</v>
+        <v>20</v>
+      </c>
+      <c r="H62" t="s">
+        <v>130</v>
       </c>
       <c r="I62" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="J62" t="s">
         <v>18</v>
@@ -2842,13 +3259,16 @@
       <c r="K62" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L62" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C63" t="s">
         <v>118</v>
@@ -2856,20 +3276,20 @@
       <c r="D63" t="s">
         <v>13</v>
       </c>
-      <c r="H63"/>
-      <c r="I63" t="s">
-        <v>18</v>
-      </c>
+      <c r="I63"/>
       <c r="J63" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K63" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+      <c r="L63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B64" t="s">
         <v>138</v>
@@ -2880,42 +3300,35 @@
       <c r="D64" t="s">
         <v>13</v>
       </c>
-      <c r="H64"/>
-      <c r="I64" t="s">
-        <v>18</v>
-      </c>
+      <c r="I64"/>
       <c r="J64" t="s">
         <v>18</v>
       </c>
       <c r="K64" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="L64" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B65" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="C65" t="s">
         <v>118</v>
       </c>
       <c r="D65" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" t="s">
-        <v>154</v>
-      </c>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5">
-        <v>46286</v>
-      </c>
-      <c r="H65" s="8">
-        <v>0.64583333333333337</v>
+        <v>20</v>
+      </c>
+      <c r="H65" t="s">
+        <v>130</v>
       </c>
       <c r="I65" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="J65" t="s">
         <v>18</v>
@@ -2923,18 +3336,19 @@
       <c r="K65" t="s">
         <v>18</v>
       </c>
+      <c r="L65" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K65" xr:uid="{187EC43D-B458-43E6-ADE2-1BE4FBEBA462}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="DIARIO"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K65">
-      <sortCondition ref="A1:A65"/>
+  <autoFilter ref="A1:L65" xr:uid="{187EC43D-B458-43E6-ADE2-1BE4FBEBA462}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L65">
+      <sortCondition ref="F1:F65"/>
     </sortState>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="E52" r:id="rId1" xr:uid="{731E922B-F779-4569-A879-856C934CB671}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
